--- a/artfynd/A 36059-2022 artfynd.xlsx
+++ b/artfynd/A 36059-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36059-2022 artfynd.xlsx
+++ b/artfynd/A 36059-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>111590552</v>
       </c>
       <c r="B2" t="n">
-        <v>57508</v>
+        <v>56272</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539224.9058763792</v>
+        <v>539224</v>
       </c>
       <c r="R2" t="n">
-        <v>6658708.536939755</v>
+        <v>6658708</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -933,149 +933,6 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>111460973</v>
-      </c>
-      <c r="B4" t="n">
-        <v>57752</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>206002</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Brunlångöra</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Plecotus auritus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Älgsjöbo, Dlr</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>539179</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6658725</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Söderbärke</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Halvt uppäten. Övre halva kroppen kvar.</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Nadja Odenhage</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Nadja Odenhage</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36059-2022 artfynd.xlsx
+++ b/artfynd/A 36059-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>111590552</v>
       </c>
       <c r="B2" t="n">
-        <v>56272</v>
+        <v>56280</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 36059-2022 artfynd.xlsx
+++ b/artfynd/A 36059-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>111590552</v>
       </c>
       <c r="B2" t="n">
-        <v>56280</v>
+        <v>56284</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 36059-2022 artfynd.xlsx
+++ b/artfynd/A 36059-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>111590552</v>
       </c>
       <c r="B2" t="n">
-        <v>56287</v>
+        <v>56292</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
